--- a/report/test_results_edit_cart_20260509_172223.xlsx
+++ b/report/test_results_edit_cart_20260509_172223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307A958B-C456-4866-B3D7-0C7B0E2A22EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1C26BD-DF58-47E4-987B-F7545DA998A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -407,8 +407,10 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0.109375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="37.6640625" customWidth="1"/>
   </cols>
   <sheetData>
